--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(3).xlsx
@@ -646,11 +646,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>charfadeout(R,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -659,7 +654,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>大卫线</t>
+      <t>sntzm_david4F(4)</t>
     </r>
     <r>
       <rPr>
@@ -667,7 +662,93 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>4</t>
+      <t>, 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=50; gotomainline=大卫线4层（终）_1</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>为了证实我被创造的意义，为了扯下人类那伪善的面具，为了求证生命与生命之间，是否可以用价值进行比较，就像那些人要求我做的那些事情一样。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=30</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>被创造？你难道不是......</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=31</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>是盖曼创造了造梦设备。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=32</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>他有些不耐烦地打断了你，似乎早就猜到你会作此一问。</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>而我，则是被创造出来控制他。只要掌握了他的思想就能掌握他的技术，很简单的道理，不是吗？</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>你到底是什么东西？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=35</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>如你所见，亚当。我是被他们利用造梦技术人为制造出来的，盖曼的另一个人格。</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>他们给我设定了公司职员的身份，给我灌输了可以靠价值大小决定人命归属的理念，给我下达了训练那些病人的任务，直到我发现这一切都是被人精心伪造的。发现自己也只是和那些病人一样，可以随意丢弃的工具。</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>所以，我突然就很想知道，除了被赋予的任务和指令外，自己这条被创造出来的生命是否拥有存在于世间的意义。以及......是否所有人类都和我的创造者一样，会用价值衡量一个人的生命。</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>困在房间里的男人咽了下口水，好为之前的长篇大论腾出一点呼吸的空间。</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>随着又一重真相的揭示，这个被捆缚在椅子上的罪人形象，在你眼中顿时变得生动而真实，因为就连他这个始作俑者也不过是受困于意义之网的另一名可悲的囚徒。</t>
+  </si>
+  <si>
+    <r>
+      <t>loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -675,7 +756,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>层（终）</t>
+      <t>sntzm_david4F(4)</t>
     </r>
     <r>
       <rPr>
@@ -683,92 +764,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_1, 1)</t>
+      <t>, 1)</t>
     </r>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=50; gotomainline=大卫线4层（终）_1</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>为了证实我被创造的意义，为了扯下人类那伪善的面具，为了求证生命与生命之间，是否可以用价值进行比较，就像那些人要求我做的那些事情一样。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=30</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>被创造？你难道不是......</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=31</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>是盖曼创造了造梦设备。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=32</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>他有些不耐烦地打断了你，似乎早就猜到你会作此一问。</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>而我，则是被创造出来控制他。只要掌握了他的思想就能掌握他的技术，很简单的道理，不是吗？</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>你到底是什么东西？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=35</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>如你所见，亚当。我是被他们利用造梦技术人为制造出来的，盖曼的另一个人格。</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>他们给我设定了公司职员的身份，给我灌输了可以靠价值大小决定人命归属的理念，给我下达了训练那些病人的任务，直到我发现这一切都是被人精心伪造的。发现自己也只是和那些病人一样，可以随意丢弃的工具。</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>所以，我突然就很想知道，除了被赋予的任务和指令外，自己这条被创造出来的生命是否拥有存在于世间的意义。以及......是否所有人类都和我的创造者一样，会用价值衡量一个人的生命。</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>困在房间里的男人咽了下口水，好为之前的长篇大论腾出一点呼吸的空间。</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>随着又一重真相的揭示，这个被捆缚在椅子上的罪人形象，在你眼中顿时变得生动而真实，因为就连他这个始作俑者也不过是受困于意义之网的另一名可悲的囚徒。</t>
-  </si>
-  <si>
-    <t>loadScript(大卫线4层（终）_1, 1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=40; gotomainline=大卫线4层（终）_1</t>
@@ -5165,7 +5162,7 @@
       <c r="J63" t="s">
         <v>15</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K63" s="3" t="s">
         <v>210</v>
       </c>
       <c r="L63" t="s">
